--- a/boc1.xlsx
+++ b/boc1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87EACD01-6603-44B7-97AB-D1C6CE65380A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73D8EEA0-2490-4333-95E2-5BE92A5159DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="1140" windowWidth="21600" windowHeight="11385" xr2:uid="{ADCE18E3-64A2-4CA2-9C29-1ED7F8C19B21}"/>
+    <workbookView xWindow="2550" yWindow="3540" windowWidth="21600" windowHeight="11385" xr2:uid="{ADCE18E3-64A2-4CA2-9C29-1ED7F8C19B21}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -439,7 +439,7 @@
   <dimension ref="A1:AK40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="13.5703125" customWidth="1"/>
+    <col min="1" max="37" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -601,51 +601,906 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.4964659999999999</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3.496346</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3.4965359999999999</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3.4964680000000001</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3.4965259999999998</v>
+      </c>
+      <c r="G3" s="2">
+        <v>3.496578</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3.4965130000000002</v>
+      </c>
+      <c r="I3" s="2">
+        <v>3.496629</v>
+      </c>
+      <c r="J3" s="2">
+        <v>3.4966599999999999</v>
+      </c>
+      <c r="K3" s="2">
+        <v>3.4967329999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.4965709999999999</v>
+      </c>
+      <c r="M3" s="2">
+        <v>3.496686</v>
+      </c>
+      <c r="N3" s="2">
+        <v>3.3608829999999998</v>
+      </c>
+      <c r="O3" s="2">
+        <v>3.349132</v>
+      </c>
+      <c r="P3" s="2">
+        <v>3.3400349999999999</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>3.3378220000000001</v>
+      </c>
+      <c r="R3" s="2">
+        <v>3.3423829999999999</v>
+      </c>
+      <c r="S3" s="2">
+        <v>3.3626179999999999</v>
+      </c>
+      <c r="T3" s="2">
+        <v>3.3529040000000001</v>
+      </c>
+      <c r="U3" s="2">
+        <v>3.3554520000000001</v>
+      </c>
+      <c r="V3" s="2">
+        <v>3.3415240000000002</v>
+      </c>
+      <c r="W3" s="2">
+        <v>3.3413010000000001</v>
+      </c>
+      <c r="X3" s="2">
+        <v>3.3511690000000001</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>3.3405209999999999</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>-0.13558300000000001</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>-0.14721400000000001</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>-0.156502</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>-0.15864600000000001</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>-0.154144</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>-0.13396</v>
+      </c>
+      <c r="AF3" s="2">
+        <v>-0.14360800000000001</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>-0.141178</v>
+      </c>
+      <c r="AH3" s="2">
+        <v>-0.155136</v>
+      </c>
+      <c r="AI3" s="2">
+        <v>-0.15543299999999999</v>
+      </c>
+      <c r="AJ3" s="2">
+        <v>-0.145403</v>
+      </c>
+      <c r="AK3" s="2">
+        <v>-0.156165</v>
+      </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3.4964659999999999</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.496346</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3.4965359999999999</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.4964680000000001</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3.4965259999999998</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3.496578</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3.4965130000000002</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3.496629</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3.4966599999999999</v>
+      </c>
+      <c r="K4" s="2">
+        <v>3.4967329999999999</v>
+      </c>
+      <c r="L4" s="2">
+        <v>3.4965709999999999</v>
+      </c>
+      <c r="M4" s="2">
+        <v>3.496686</v>
+      </c>
+      <c r="N4" s="2">
+        <v>3.4764089999999999</v>
+      </c>
+      <c r="O4" s="2">
+        <v>3.4752350000000001</v>
+      </c>
+      <c r="P4" s="2">
+        <v>3.4736030000000002</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>3.4736210000000001</v>
+      </c>
+      <c r="R4" s="2">
+        <v>3.4739900000000001</v>
+      </c>
+      <c r="S4" s="2">
+        <v>3.4769950000000001</v>
+      </c>
+      <c r="T4" s="2">
+        <v>3.4752160000000001</v>
+      </c>
+      <c r="U4" s="2">
+        <v>3.476178</v>
+      </c>
+      <c r="V4" s="2">
+        <v>3.4744160000000002</v>
+      </c>
+      <c r="W4" s="2">
+        <v>3.4743029999999999</v>
+      </c>
+      <c r="X4" s="2">
+        <v>3.4752779999999999</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>3.4744229999999998</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>-2.0056999999999998E-2</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>-2.1111000000000001E-2</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>-2.2932999999999999E-2</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>-2.2846999999999999E-2</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>-2.2537000000000001E-2</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>-1.9583E-2</v>
+      </c>
+      <c r="AF4" s="2">
+        <v>-2.1295999999999999E-2</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>-2.0451E-2</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>-2.2244E-2</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>-2.2429999999999999E-2</v>
+      </c>
+      <c r="AJ4" s="2">
+        <v>-2.1292999999999999E-2</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>-2.2263000000000002E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="2">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3.4964659999999999</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.496346</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3.4965359999999999</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.4964680000000001</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3.4965259999999998</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3.496578</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3.4965130000000002</v>
+      </c>
+      <c r="I5" s="2">
+        <v>3.496629</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3.4966599999999999</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3.4967329999999999</v>
+      </c>
+      <c r="L5" s="2">
+        <v>3.4965709999999999</v>
+      </c>
+      <c r="M5" s="2">
+        <v>3.496686</v>
+      </c>
+      <c r="N5" s="2">
+        <v>3.488356</v>
+      </c>
+      <c r="O5" s="2">
+        <v>3.4881160000000002</v>
+      </c>
+      <c r="P5" s="2">
+        <v>3.4881579999999999</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>3.4881470000000001</v>
+      </c>
+      <c r="R5" s="2">
+        <v>3.4881890000000002</v>
+      </c>
+      <c r="S5" s="2">
+        <v>3.48847</v>
+      </c>
+      <c r="T5" s="2">
+        <v>3.4883389999999999</v>
+      </c>
+      <c r="U5" s="2">
+        <v>3.4885069999999998</v>
+      </c>
+      <c r="V5" s="2">
+        <v>3.4883229999999998</v>
+      </c>
+      <c r="W5" s="2">
+        <v>3.488632</v>
+      </c>
+      <c r="X5" s="2">
+        <v>3.488299</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>3.4885540000000002</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>-8.1089999999999999E-3</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>-8.2299999999999995E-3</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>-8.3789999999999993E-3</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>-8.3210000000000003E-3</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>-8.3370000000000007E-3</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>-8.1080000000000006E-3</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>-8.1740000000000007E-3</v>
+      </c>
+      <c r="AG5" s="2">
+        <v>-8.123E-3</v>
+      </c>
+      <c r="AH5" s="2">
+        <v>-8.3370000000000007E-3</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>-8.1010000000000006E-3</v>
+      </c>
+      <c r="AJ5" s="2">
+        <v>-8.2719999999999998E-3</v>
+      </c>
+      <c r="AK5" s="2">
+        <v>-8.1309999999999993E-3</v>
+      </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="2">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3.4963649999999999</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3.4964650000000002</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3.496356</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.4963920000000002</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3.4964460000000002</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3.4964849999999998</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3.496556</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3.4966029999999999</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3.4964119999999999</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3.496302</v>
+      </c>
+      <c r="L6" s="2">
+        <v>3.4963519999999999</v>
+      </c>
+      <c r="M6" s="2">
+        <v>3.4964119999999999</v>
+      </c>
+      <c r="N6" s="2">
+        <v>3.4889890000000001</v>
+      </c>
+      <c r="O6" s="2">
+        <v>3.488998</v>
+      </c>
+      <c r="P6" s="2">
+        <v>3.4889299999999999</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>3.4889510000000001</v>
+      </c>
+      <c r="R6" s="2">
+        <v>3.48908</v>
+      </c>
+      <c r="S6" s="2">
+        <v>3.4893100000000001</v>
+      </c>
+      <c r="T6" s="2">
+        <v>3.4893390000000002</v>
+      </c>
+      <c r="U6" s="2">
+        <v>3.489309</v>
+      </c>
+      <c r="V6" s="2">
+        <v>3.489109</v>
+      </c>
+      <c r="W6" s="2">
+        <v>3.4892439999999998</v>
+      </c>
+      <c r="X6" s="2">
+        <v>3.4890379999999999</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>3.4892189999999998</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>-7.3759999999999997E-3</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>-7.4660000000000004E-3</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>-7.4260000000000003E-3</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>-7.4419999999999998E-3</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>-7.3660000000000002E-3</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>-7.175E-3</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>-7.2170000000000003E-3</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>-7.2940000000000001E-3</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>-7.3020000000000003E-3</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>-7.0590000000000002E-3</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>-7.3130000000000001E-3</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>-7.1929999999999997E-3</v>
+      </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="2">
+        <v>160</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3.4956070000000001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3.495593</v>
+      </c>
       <c r="D7" s="2">
-        <v>4</v>
+        <v>3.4956990000000001</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3.495727</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3.4958300000000002</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3.4957769999999999</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3.495679</v>
+      </c>
+      <c r="I7" s="2">
+        <v>3.4955919999999998</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3.4957129999999998</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3.4956339999999999</v>
+      </c>
+      <c r="L7" s="2">
+        <v>3.495622</v>
+      </c>
+      <c r="M7" s="2">
+        <v>3.495549</v>
+      </c>
+      <c r="N7" s="2">
+        <v>3.489214</v>
+      </c>
+      <c r="O7" s="2">
+        <v>3.4891619999999999</v>
+      </c>
+      <c r="P7" s="2">
+        <v>3.4893399999999999</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>3.4894889999999998</v>
+      </c>
+      <c r="R7" s="2">
+        <v>3.4894620000000001</v>
+      </c>
+      <c r="S7" s="2">
+        <v>3.4896259999999999</v>
+      </c>
+      <c r="T7" s="2">
+        <v>3.4895260000000001</v>
+      </c>
+      <c r="U7" s="2">
+        <v>3.489392</v>
+      </c>
+      <c r="V7" s="2">
+        <v>3.4893939999999999</v>
+      </c>
+      <c r="W7" s="2">
+        <v>3.4895939999999999</v>
+      </c>
+      <c r="X7" s="2">
+        <v>3.489433</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>3.4895499999999999</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>-6.3920000000000001E-3</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>-6.43E-3</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>-6.3590000000000001E-3</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>-6.2389999999999998E-3</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>-6.3680000000000004E-3</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>-6.1510000000000002E-3</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>-6.1529999999999996E-3</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>-6.1999999999999998E-3</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>-6.319E-3</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>-6.0410000000000004E-3</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>-6.1890000000000001E-3</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>-5.999E-3</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>2500</v>
+      </c>
+      <c r="B8" s="2">
+        <v>3.496553</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3.4966520000000001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3.4965549999999999</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3.4964979999999999</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3.4965380000000001</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3.496721</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3.496537</v>
+      </c>
+      <c r="I8" s="2">
+        <v>3.496429</v>
+      </c>
+      <c r="J8" s="2">
+        <v>3.4965030000000001</v>
+      </c>
+      <c r="K8" s="2">
+        <v>3.4964900000000001</v>
+      </c>
+      <c r="L8" s="2">
+        <v>3.4967290000000002</v>
+      </c>
+      <c r="M8" s="2">
+        <v>3.4964919999999999</v>
+      </c>
+      <c r="N8" s="2">
+        <v>3.4919310000000001</v>
+      </c>
+      <c r="O8" s="2">
+        <v>3.4920529999999999</v>
+      </c>
+      <c r="P8" s="2">
+        <v>3.4927190000000001</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>3.4920680000000002</v>
+      </c>
+      <c r="R8" s="2">
+        <v>3.4922260000000001</v>
+      </c>
+      <c r="S8" s="2">
+        <v>3.4920049999999998</v>
+      </c>
+      <c r="T8" s="2">
+        <v>3.4938250000000002</v>
+      </c>
+      <c r="U8" s="2">
+        <v>3.49187</v>
+      </c>
+      <c r="V8" s="2">
+        <v>3.4916849999999999</v>
+      </c>
+      <c r="W8" s="2">
+        <v>3.492359</v>
+      </c>
+      <c r="X8" s="2">
+        <v>3.492661</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>3.492083</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>-4.6220000000000002E-3</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>-4.5999999999999999E-3</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>-3.8349999999999999E-3</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>-4.4299999999999999E-3</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>-4.3119999999999999E-3</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>-4.7159999999999997E-3</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>-2.712E-3</v>
+      </c>
+      <c r="AG8" s="2">
+        <v>-4.5589999999999997E-3</v>
+      </c>
+      <c r="AH8" s="2">
+        <v>-4.8180000000000002E-3</v>
+      </c>
+      <c r="AI8" s="2">
+        <v>-4.1310000000000001E-3</v>
+      </c>
+      <c r="AJ8" s="2">
+        <v>-4.0670000000000003E-3</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>-4.4089999999999997E-3</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>4600</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3.4971299999999998</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3.4971960000000002</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3.4972919999999998</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.496947</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3.4970469999999998</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3.496931</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3.4972500000000002</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3.4970279999999998</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3.4971399999999999</v>
+      </c>
+      <c r="K9" s="2">
+        <v>3.4972219999999998</v>
+      </c>
+      <c r="L9" s="2">
+        <v>3.4970650000000001</v>
+      </c>
+      <c r="M9" s="2">
+        <v>3.4971320000000001</v>
+      </c>
+      <c r="N9" s="2">
+        <v>3.4829859999999999</v>
+      </c>
+      <c r="O9" s="2">
+        <v>3.4832459999999998</v>
+      </c>
+      <c r="P9" s="2">
+        <v>3.4851209999999999</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>3.4833210000000001</v>
+      </c>
+      <c r="R9" s="2">
+        <v>3.4835980000000002</v>
+      </c>
+      <c r="S9" s="2">
+        <v>3.4824130000000002</v>
+      </c>
+      <c r="T9" s="2">
+        <v>3.4884119999999998</v>
+      </c>
+      <c r="U9" s="2">
+        <v>3.482415</v>
+      </c>
+      <c r="V9" s="2">
+        <v>3.4815860000000001</v>
+      </c>
+      <c r="W9" s="2">
+        <v>3.4834589999999999</v>
+      </c>
+      <c r="X9" s="2">
+        <v>3.4849100000000002</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>3.4829699999999999</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>-1.4144E-2</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>-1.3950000000000001E-2</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>-1.2171E-2</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>-1.3625999999999999E-2</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>-1.3448999999999999E-2</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>-1.4517E-2</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>-8.8369999999999994E-3</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>-1.4612E-2</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>-1.5554999999999999E-2</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>-1.3762999999999999E-2</v>
+      </c>
+      <c r="AJ9" s="2">
+        <v>-1.2154999999999999E-2</v>
+      </c>
+      <c r="AK9" s="2">
+        <v>-1.4161E-2</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>4800</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3.497293</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.4972409999999998</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3.4971800000000002</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3.4973230000000002</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3.4972180000000002</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3.497074</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3.4972249999999998</v>
+      </c>
+      <c r="I10" s="2">
+        <v>3.4971649999999999</v>
+      </c>
+      <c r="J10" s="2">
+        <v>3.4972059999999998</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3.4971700000000001</v>
+      </c>
+      <c r="L10" s="2">
+        <v>3.497255</v>
+      </c>
+      <c r="M10" s="2">
+        <v>3.4911799999999999</v>
+      </c>
+      <c r="N10" s="2">
+        <v>3.206251</v>
+      </c>
+      <c r="O10" s="2">
+        <v>3.2063890000000002</v>
+      </c>
+      <c r="P10" s="2">
+        <v>3.2083590000000002</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>3.2065990000000002</v>
+      </c>
+      <c r="R10" s="2">
+        <v>3.2070159999999999</v>
+      </c>
+      <c r="S10" s="2">
+        <v>3.2055220000000002</v>
+      </c>
+      <c r="T10" s="2">
+        <v>3.2116479999999998</v>
+      </c>
+      <c r="U10" s="2">
+        <v>3.2056040000000001</v>
+      </c>
+      <c r="V10" s="2">
+        <v>3.2048540000000001</v>
+      </c>
+      <c r="W10" s="2">
+        <v>3.2066509999999999</v>
+      </c>
+      <c r="X10" s="2">
+        <v>3.2080649999999999</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>3.2061869999999999</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>-0.29104200000000002</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>-0.29085299999999997</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>-0.28882099999999999</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>-0.29072399999999998</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>-0.29020200000000002</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>-0.29155199999999998</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>-0.28557700000000003</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>-0.29156100000000001</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>-0.292352</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>-0.29051900000000003</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>-0.28919</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>-0.284993</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.25">
@@ -807,43 +1662,681 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="B15" s="2">
+        <v>5.3319999999999999E-3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>5.339E-3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>5.3340000000000002E-3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.3280000000000003E-3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5.3369999999999997E-3</v>
+      </c>
+      <c r="G15" s="3">
+        <v>5.3319999999999999E-3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>5.3530000000000001E-3</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5.3449999999999999E-3</v>
+      </c>
+      <c r="J15" s="3">
+        <v>5.3530000000000001E-3</v>
+      </c>
+      <c r="K15" s="3">
+        <v>5.3470000000000002E-3</v>
+      </c>
+      <c r="L15" s="3">
+        <v>5.3400000000000001E-3</v>
+      </c>
+      <c r="M15" s="3">
+        <v>5.3369999999999997E-3</v>
+      </c>
+      <c r="N15" s="3">
+        <v>5.0179999999999999E-3</v>
+      </c>
+      <c r="O15" s="3">
+        <v>4.9740000000000001E-3</v>
+      </c>
+      <c r="P15" s="3">
+        <v>4.9940000000000002E-3</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>5.0229999999999997E-3</v>
+      </c>
+      <c r="R15" s="3">
+        <v>4.9769999999999997E-3</v>
+      </c>
+      <c r="S15" s="3">
+        <v>4.9670000000000001E-3</v>
+      </c>
+      <c r="T15" s="3">
+        <v>4.9670000000000001E-3</v>
+      </c>
+      <c r="U15" s="3">
+        <v>4.9589999999999999E-3</v>
+      </c>
+      <c r="V15" s="3">
+        <v>4.973E-3</v>
+      </c>
+      <c r="W15" s="3">
+        <v>4.9569999999999996E-3</v>
+      </c>
+      <c r="X15" s="3">
+        <v>4.9620000000000003E-3</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>4.9659999999999999E-3</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>-3.1399999999999999E-4</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>-3.6499999999999998E-4</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>-3.4000000000000002E-4</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>-3.0499999999999999E-4</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>-3.6000000000000002E-4</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>-3.6499999999999998E-4</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>-3.8699999999999997E-4</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>-3.86E-4</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>-3.8000000000000002E-4</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>-3.8999999999999999E-4</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>-3.7800000000000003E-4</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>-3.7100000000000002E-4</v>
+      </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="A16" s="2">
+        <v>160</v>
+      </c>
+      <c r="B16" s="2">
+        <v>9.9143999999999996E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>9.9154999999999993E-2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.7469999999999999E-3</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.5869999999999999E-3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>9.9127999999999994E-2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>9.9129999999999996E-2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>9.9132999999999999E-2</v>
+      </c>
+      <c r="I16" s="3">
+        <v>9.9134E-2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>9.9134E-2</v>
+      </c>
+      <c r="K16" s="3">
+        <v>9.9132999999999999E-2</v>
+      </c>
+      <c r="L16" s="3">
+        <v>9.9129999999999996E-2</v>
+      </c>
+      <c r="M16" s="3">
+        <v>9.9132999999999999E-2</v>
+      </c>
+      <c r="N16" s="3">
+        <v>9.9070000000000005E-2</v>
+      </c>
+      <c r="O16" s="3">
+        <v>9.9072999999999994E-2</v>
+      </c>
+      <c r="P16" s="3">
+        <v>2.1320000000000002E-3</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>2.196E-3</v>
+      </c>
+      <c r="R16" s="3">
+        <v>9.9051E-2</v>
+      </c>
+      <c r="S16" s="3">
+        <v>9.9059999999999995E-2</v>
+      </c>
+      <c r="T16" s="3">
+        <v>9.9058999999999994E-2</v>
+      </c>
+      <c r="U16" s="3">
+        <v>9.9057999999999993E-2</v>
+      </c>
+      <c r="V16" s="3">
+        <v>9.9058999999999994E-2</v>
+      </c>
+      <c r="W16" s="3">
+        <v>9.9065E-2</v>
+      </c>
+      <c r="X16" s="3">
+        <v>9.9060999999999996E-2</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>9.9068000000000003E-2</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>-7.3999999999999996E-5</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>-8.2000000000000001E-5</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>-6.1499999999999999E-4</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>-3.9100000000000002E-4</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>-7.7000000000000001E-5</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>-6.9999999999999994E-5</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>-7.3999999999999996E-5</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>-7.6000000000000004E-5</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>-7.4999999999999993E-5</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>-6.7999999999999999E-5</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>-6.8999999999999997E-5</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>-6.4999999999999994E-5</v>
+      </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="2">
+        <v>160</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.99717100000000003</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.99716199999999999</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.99725799999999998</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.99723600000000001</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.99729900000000005</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.99730700000000005</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.99724699999999999</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.99727500000000002</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.99728399999999995</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.99725600000000003</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.99733099999999997</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.99732699999999996</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.996726</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.99670499999999995</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.99678599999999995</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.99683299999999997</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.99683699999999997</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.99691200000000002</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0.99687000000000003</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.99683600000000006</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.99685599999999996</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.99689000000000005</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.99689300000000003</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.99699199999999999</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>-4.46E-4</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>-4.57E-4</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>-4.7199999999999998E-4</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>-4.0299999999999998E-4</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>-4.6200000000000001E-4</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>-3.9599999999999998E-4</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>-3.77E-4</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>-4.3899999999999999E-4</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>-4.28E-4</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>-3.6600000000000001E-4</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>-4.3800000000000002E-4</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>-3.3500000000000001E-4</v>
+      </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4.9432</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4.9435000000000002</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4.9428999999999998</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4.9433999999999996</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4.9427000000000003</v>
+      </c>
+      <c r="G18" s="3">
+        <v>4.9432</v>
+      </c>
+      <c r="H18" s="3">
+        <v>4.9436999999999998</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4.9432999999999998</v>
+      </c>
+      <c r="J18" s="3">
+        <v>4.9432</v>
+      </c>
+      <c r="K18" s="3">
+        <v>4.9432999999999998</v>
+      </c>
+      <c r="L18" s="3">
+        <v>4.9436</v>
+      </c>
+      <c r="M18" s="3">
+        <v>4.9435000000000002</v>
+      </c>
+      <c r="N18" s="3">
+        <v>4.9428000000000001</v>
+      </c>
+      <c r="O18" s="3">
+        <v>4.9429999999999996</v>
+      </c>
+      <c r="P18" s="3">
+        <v>4.9428999999999998</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>4.9429999999999996</v>
+      </c>
+      <c r="R18" s="3">
+        <v>4.9428000000000001</v>
+      </c>
+      <c r="S18" s="3">
+        <v>4.9432</v>
+      </c>
+      <c r="T18" s="3">
+        <v>4.9436</v>
+      </c>
+      <c r="U18" s="3">
+        <v>4.9438000000000004</v>
+      </c>
+      <c r="V18" s="3">
+        <v>4.9431000000000003</v>
+      </c>
+      <c r="W18" s="3">
+        <v>4.9435000000000002</v>
+      </c>
+      <c r="X18" s="3">
+        <v>4.9435000000000002</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>4.9436999999999998</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-4.0000000000000002E-4</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-4.0000000000000002E-4</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-2.9999999999999997E-4</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>-1E-4</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>-1E-4</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>-1E-4</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>2.0000000000000001E-4</v>
+      </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="A19" s="3">
+        <v>160</v>
+      </c>
+      <c r="B19" s="3">
+        <v>10.0093</v>
+      </c>
+      <c r="C19" s="3">
+        <v>10.009600000000001</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10.0092</v>
+      </c>
+      <c r="E19" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="F19" s="3">
+        <v>10.0097</v>
+      </c>
+      <c r="G19" s="3">
+        <v>10.010199999999999</v>
+      </c>
+      <c r="H19" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="I19" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="J19" s="3">
+        <v>10.0097</v>
+      </c>
+      <c r="K19" s="3">
+        <v>10.010300000000001</v>
+      </c>
+      <c r="L19" s="3">
+        <v>10.010199999999999</v>
+      </c>
+      <c r="M19" s="3">
+        <v>10.0106</v>
+      </c>
+      <c r="N19" s="3">
+        <v>10.008599999999999</v>
+      </c>
+      <c r="O19" s="3">
+        <v>10.010400000000001</v>
+      </c>
+      <c r="P19" s="3">
+        <v>10.0099</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>10.0105</v>
+      </c>
+      <c r="R19" s="3">
+        <v>10.010300000000001</v>
+      </c>
+      <c r="S19" s="3">
+        <v>10.0098</v>
+      </c>
+      <c r="T19" s="3">
+        <v>10.0115</v>
+      </c>
+      <c r="U19" s="3">
+        <v>10.012600000000001</v>
+      </c>
+      <c r="V19" s="3">
+        <v>10.010199999999999</v>
+      </c>
+      <c r="W19" s="3">
+        <v>10.011100000000001</v>
+      </c>
+      <c r="X19" s="3">
+        <v>10.0116</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>10.010199999999999</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>-6.9999999999999999E-4</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>-4.0000000000000002E-4</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AK19" s="3">
+        <v>-4.0000000000000002E-4</v>
+      </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="A20" s="3">
+        <v>160</v>
+      </c>
+      <c r="B20" s="3">
+        <v>14.065899999999999</v>
+      </c>
+      <c r="C20" s="3">
+        <v>14.064500000000001</v>
+      </c>
+      <c r="D20" s="3">
+        <v>14.064399999999999</v>
+      </c>
+      <c r="E20" s="3">
+        <v>14.0649</v>
+      </c>
+      <c r="F20" s="3">
+        <v>14.0641</v>
+      </c>
+      <c r="G20" s="3">
+        <v>14.0626</v>
+      </c>
+      <c r="H20" s="3">
+        <v>14.0646</v>
+      </c>
+      <c r="I20" s="3">
+        <v>14.064399999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>14.0655</v>
+      </c>
+      <c r="K20" s="3">
+        <v>14.063800000000001</v>
+      </c>
+      <c r="L20" s="3">
+        <v>14.065099999999999</v>
+      </c>
+      <c r="M20" s="3">
+        <v>14.0655</v>
+      </c>
+      <c r="N20" s="3">
+        <v>14.0609</v>
+      </c>
+      <c r="O20" s="3">
+        <v>14.065200000000001</v>
+      </c>
+      <c r="P20" s="3">
+        <v>14.0642</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>14.064299999999999</v>
+      </c>
+      <c r="R20" s="3">
+        <v>14.064299999999999</v>
+      </c>
+      <c r="S20" s="3">
+        <v>14.061</v>
+      </c>
+      <c r="T20" s="3">
+        <v>14.066599999999999</v>
+      </c>
+      <c r="U20" s="3">
+        <v>14.069599999999999</v>
+      </c>
+      <c r="V20" s="3">
+        <v>14.0648</v>
+      </c>
+      <c r="W20" s="3">
+        <v>14.0656</v>
+      </c>
+      <c r="X20" s="3">
+        <v>14.067399999999999</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>14.063700000000001</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-4.8999999999999998E-3</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>-1E-4</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>-5.0000000000000001E-4</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-1.6999999999999999E-3</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>-6.9999999999999999E-4</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>-1.8E-3</v>
+      </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
@@ -1012,59 +2505,1379 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+        <v>-20</v>
+      </c>
+      <c r="B25" s="2">
+        <v>-18.746296000000001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-18.750138</v>
+      </c>
+      <c r="D25" s="2">
+        <v>-18.748308999999999</v>
+      </c>
+      <c r="E25" s="3">
+        <v>-18.755163</v>
+      </c>
+      <c r="F25" s="3">
+        <v>-18.75581</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-18.750941000000001</v>
+      </c>
+      <c r="H25" s="3">
+        <v>-18.75245</v>
+      </c>
+      <c r="I25" s="3">
+        <v>-18.743162000000002</v>
+      </c>
+      <c r="J25" s="3">
+        <v>-18.751308999999999</v>
+      </c>
+      <c r="K25" s="3">
+        <v>-18.749077</v>
+      </c>
+      <c r="L25" s="3">
+        <v>-18.750499000000001</v>
+      </c>
+      <c r="M25" s="3">
+        <v>-18.759867</v>
+      </c>
+      <c r="N25" s="3">
+        <v>18.620574999999999</v>
+      </c>
+      <c r="O25" s="3">
+        <v>18.632404000000001</v>
+      </c>
+      <c r="P25" s="3">
+        <v>18.629147</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>18.636057000000001</v>
+      </c>
+      <c r="R25" s="3">
+        <v>18.633870999999999</v>
+      </c>
+      <c r="S25" s="3">
+        <v>18.630507000000001</v>
+      </c>
+      <c r="T25" s="3">
+        <v>18.637001000000001</v>
+      </c>
+      <c r="U25" s="3">
+        <v>18.632964999999999</v>
+      </c>
+      <c r="V25" s="3">
+        <v>18.633617000000001</v>
+      </c>
+      <c r="W25" s="3">
+        <v>18.633686000000001</v>
+      </c>
+      <c r="X25" s="3">
+        <v>18.633973999999998</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>18.63636</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>-0.125721</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>-0.117733</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>-0.119162</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>-0.119106</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>-0.12193900000000001</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>-0.120434</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>-0.115449</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>-0.110197</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>-0.117691</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>-0.11539099999999999</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>-0.116525</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>-0.12350700000000001</v>
+      </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="A26" s="2">
+        <v>-15</v>
+      </c>
+      <c r="B26" s="2">
+        <v>-14.065289999999999</v>
+      </c>
+      <c r="C26" s="2">
+        <v>-14.073086</v>
+      </c>
+      <c r="D26" s="2">
+        <v>-14.072843000000001</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-14.077779</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-14.074593999999999</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-14.066034999999999</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-14.068085999999999</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-14.067205</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-14.074322</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-14.073198</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-14.071904</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-14.079580999999999</v>
+      </c>
+      <c r="N26" s="3">
+        <v>13.971874</v>
+      </c>
+      <c r="O26" s="3">
+        <v>13.982519999999999</v>
+      </c>
+      <c r="P26" s="3">
+        <v>13.980626000000001</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>13.985246</v>
+      </c>
+      <c r="R26" s="3">
+        <v>13.981666000000001</v>
+      </c>
+      <c r="S26" s="3">
+        <v>13.973801999999999</v>
+      </c>
+      <c r="T26" s="3">
+        <v>13.978584</v>
+      </c>
+      <c r="U26" s="3">
+        <v>13.980793999999999</v>
+      </c>
+      <c r="V26" s="3">
+        <v>13.981906</v>
+      </c>
+      <c r="W26" s="3">
+        <v>13.982521</v>
+      </c>
+      <c r="X26" s="3">
+        <v>13.981102</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>13.987042000000001</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-9.3414999999999998E-2</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-9.0565999999999994E-2</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>-9.2216999999999993E-2</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>-9.2533000000000004E-2</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-9.2927999999999997E-2</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-9.2233999999999997E-2</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-8.9501999999999998E-2</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>-8.6411000000000002E-2</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-9.2415999999999998E-2</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>-9.0676999999999994E-2</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>-9.0801999999999994E-2</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>-9.2537999999999995E-2</v>
+      </c>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="A27" s="2">
+        <v>-10</v>
+      </c>
+      <c r="B27" s="2">
+        <v>-9.3614139999999999</v>
+      </c>
+      <c r="C27" s="2">
+        <v>-9.3651239999999998</v>
+      </c>
+      <c r="D27" s="2">
+        <v>-9.3643239999999999</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9.3682820000000007</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-9.3653250000000003</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-9.3612380000000002</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-9.3622200000000007</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-9.3620040000000007</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-9.3661159999999999</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-9.3649299999999993</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-9.3640670000000004</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-9.3702710000000007</v>
+      </c>
+      <c r="N27" s="3">
+        <v>9.2988710000000001</v>
+      </c>
+      <c r="O27" s="3">
+        <v>9.3045709999999993</v>
+      </c>
+      <c r="P27" s="3">
+        <v>9.3043469999999999</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>9.3016229999999993</v>
+      </c>
+      <c r="R27" s="3">
+        <v>9.2970419999999994</v>
+      </c>
+      <c r="S27" s="3">
+        <v>9.2942370000000007</v>
+      </c>
+      <c r="T27" s="3">
+        <v>9.2972090000000005</v>
+      </c>
+      <c r="U27" s="3">
+        <v>9.2977229999999995</v>
+      </c>
+      <c r="V27" s="3">
+        <v>9.2997560000000004</v>
+      </c>
+      <c r="W27" s="3">
+        <v>9.2997599999999991</v>
+      </c>
+      <c r="X27" s="3">
+        <v>9.2983720000000005</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>9.3037980000000005</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-6.2543000000000001E-2</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-6.0553000000000003E-2</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-5.9977000000000003E-2</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>-6.6658999999999996E-2</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-6.8282999999999996E-2</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>-6.7001000000000005E-2</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>-6.5010999999999999E-2</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>-6.4282000000000006E-2</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-6.6360000000000002E-2</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>-6.5170000000000006E-2</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>-6.5695000000000003E-2</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>-6.6473000000000004E-2</v>
+      </c>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="A28" s="2">
+        <v>-5</v>
+      </c>
+      <c r="B28" s="2">
+        <v>-4.6712829999999999</v>
+      </c>
+      <c r="C28" s="2">
+        <v>-4.6739990000000002</v>
+      </c>
       <c r="D28" s="2">
-        <v>4</v>
+        <v>-4.6741960000000002</v>
+      </c>
+      <c r="E28" s="3">
+        <v>-4.6748919999999998</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-4.6745099999999997</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-4.6714849999999997</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-4.6726739999999998</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-4.6724300000000003</v>
+      </c>
+      <c r="J28" s="3">
+        <v>-4.6747269999999999</v>
+      </c>
+      <c r="K28" s="3">
+        <v>-4.6743119999999996</v>
+      </c>
+      <c r="L28" s="3">
+        <v>-4.6737460000000004</v>
+      </c>
+      <c r="M28" s="3">
+        <v>-4.6757629999999999</v>
+      </c>
+      <c r="N28" s="3">
+        <v>4.6376520000000001</v>
+      </c>
+      <c r="O28" s="3">
+        <v>4.6410239999999998</v>
+      </c>
+      <c r="P28" s="3">
+        <v>4.6412170000000001</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>4.642334</v>
+      </c>
+      <c r="R28" s="3">
+        <v>4.640784</v>
+      </c>
+      <c r="S28" s="3">
+        <v>4.6379010000000003</v>
+      </c>
+      <c r="T28" s="3">
+        <v>4.6402720000000004</v>
+      </c>
+      <c r="U28" s="3">
+        <v>4.6396649999999999</v>
+      </c>
+      <c r="V28" s="3">
+        <v>4.6414439999999999</v>
+      </c>
+      <c r="W28" s="3">
+        <v>4.6416130000000004</v>
+      </c>
+      <c r="X28" s="3">
+        <v>4.6403400000000001</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>4.6430490000000004</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>-3.3631000000000001E-2</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>-3.2974999999999997E-2</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>-3.2979000000000001E-2</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>-3.2557999999999997E-2</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>-3.3725999999999999E-2</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>-3.3583000000000002E-2</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>-3.2400999999999999E-2</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>-3.2765000000000002E-2</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>-3.3283E-2</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>-3.2698999999999999E-2</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>-3.3405999999999998E-2</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>-3.2714E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>-1</v>
+      </c>
+      <c r="B29" s="3">
+        <v>-0.91401900000000003</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-0.91472299999999995</v>
+      </c>
+      <c r="D29" s="3">
+        <v>-0.914601</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-0.91500400000000004</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-0.914798</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-0.91421600000000003</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-0.91464400000000001</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-0.91457699999999997</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-0.91483899999999996</v>
+      </c>
+      <c r="K29" s="3">
+        <v>-0.91488899999999995</v>
+      </c>
+      <c r="L29" s="3">
+        <v>-0.91471100000000005</v>
+      </c>
+      <c r="M29" s="3">
+        <v>-0.91524899999999998</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0.90661400000000003</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0.90833900000000001</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0.90866800000000003</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0.90944499999999995</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0.90774699999999997</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0.90737500000000004</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0.90761400000000003</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0.90784900000000002</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0.90797300000000003</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0.90819000000000005</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0.90786900000000004</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0.90899200000000002</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>-7.4050000000000001E-3</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>-6.3829999999999998E-3</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>-5.9329999999999999E-3</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>-5.5589999999999997E-3</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>-7.051E-3</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>-6.8399999999999997E-3</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>-7.0299999999999998E-3</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>-6.7279999999999996E-3</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>-6.8659999999999997E-3</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>-6.7000000000000002E-3</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>-6.8430000000000001E-3</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>-6.2570000000000004E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="B30" s="3">
+        <v>-8.2667000000000004E-2</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-8.2728999999999997E-2</v>
+      </c>
+      <c r="D30" s="3">
+        <v>-8.2708000000000004E-2</v>
+      </c>
+      <c r="E30" s="3">
+        <v>-8.2669000000000006E-2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>-8.2637000000000002E-2</v>
+      </c>
+      <c r="G30" s="3">
+        <v>-8.2507999999999998E-2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>-8.2641999999999993E-2</v>
+      </c>
+      <c r="I30" s="3">
+        <v>-8.2765000000000005E-2</v>
+      </c>
+      <c r="J30" s="3">
+        <v>-8.2820000000000005E-2</v>
+      </c>
+      <c r="K30" s="3">
+        <v>-8.2822999999999994E-2</v>
+      </c>
+      <c r="L30" s="3">
+        <v>-8.2730999999999999E-2</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-8.2693000000000003E-2</v>
+      </c>
+      <c r="N30" s="3">
+        <v>8.1381999999999996E-2</v>
+      </c>
+      <c r="O30" s="3">
+        <v>8.2711000000000007E-2</v>
+      </c>
+      <c r="P30" s="3">
+        <v>8.2905000000000006E-2</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>8.3313999999999999E-2</v>
+      </c>
+      <c r="R30" s="3">
+        <v>8.1785999999999998E-2</v>
+      </c>
+      <c r="S30" s="3">
+        <v>8.1851999999999994E-2</v>
+      </c>
+      <c r="T30" s="3">
+        <v>8.1836999999999993E-2</v>
+      </c>
+      <c r="U30" s="3">
+        <v>8.2030000000000006E-2</v>
+      </c>
+      <c r="V30" s="3">
+        <v>8.2142999999999994E-2</v>
+      </c>
+      <c r="W30" s="3">
+        <v>8.2295999999999994E-2</v>
+      </c>
+      <c r="X30" s="3">
+        <v>8.183E-2</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>8.2601999999999995E-2</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>-1.286E-3</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>-1.8E-5</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>1.9699999999999999E-4</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>6.4499999999999996E-4</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>-8.5099999999999998E-4</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>-6.5600000000000001E-4</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>-8.0500000000000005E-4</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>-7.3499999999999998E-4</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>-6.78E-4</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>-5.2800000000000004E-4</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>-9.01E-4</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>-9.1000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.107608</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.107284</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.107575</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.107641</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.107346</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0.107457</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.107599</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0.107338</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.107692</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0.107679</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0.10739799999999999</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0.107623</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0.107527</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0.10634200000000001</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0.106279</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0.106169</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0.107206</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0.107292</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0.107018</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0.107044</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0.10707899999999999</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0.10691100000000001</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0.107263</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0.10693999999999999</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>-8.1000000000000004E-5</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>-9.4200000000000002E-4</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>-1.2960000000000001E-3</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>-1.4710000000000001E-3</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>-1.3999999999999999E-4</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>-1.65E-4</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>-5.8200000000000005E-4</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>-2.9500000000000001E-4</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>-6.1200000000000002E-4</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>-7.6800000000000002E-4</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>-1.35E-4</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>-6.8300000000000001E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>1</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.97008899999999998</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.970553</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.97064399999999995</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.97065599999999996</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.97062000000000004</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0.97026000000000001</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0.97047600000000001</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0.97047899999999998</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.97042300000000004</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0.97033100000000005</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0.97028899999999996</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0.97107500000000002</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0.96442799999999995</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0.96372599999999997</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0.96345099999999995</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0.96363500000000002</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0.96484999999999999</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0.96415499999999998</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0.96426999999999996</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0.96412900000000001</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0.96444600000000003</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0.96403300000000003</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0.96426500000000004</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0.964306</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-5.6600000000000001E-3</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-6.8269999999999997E-3</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-7.1929999999999997E-3</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-7.0210000000000003E-3</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-5.77E-3</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>-6.1040000000000001E-3</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-6.2059999999999997E-3</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>-6.3499999999999997E-3</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>-5.9760000000000004E-3</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>-6.2979999999999998E-3</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>-6.0239999999999998E-3</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>-6.7689999999999998E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3">
+        <v>4.7169020000000002</v>
+      </c>
+      <c r="C33" s="3">
+        <v>4.7168770000000002</v>
+      </c>
+      <c r="D33" s="3">
+        <v>4.7164590000000004</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4.7176150000000003</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4.71706</v>
+      </c>
+      <c r="G33" s="3">
+        <v>4.7152520000000004</v>
+      </c>
+      <c r="H33" s="3">
+        <v>4.7151670000000001</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4.7161660000000003</v>
+      </c>
+      <c r="J33" s="3">
+        <v>4.7178149999999999</v>
+      </c>
+      <c r="K33" s="3">
+        <v>4.7165609999999996</v>
+      </c>
+      <c r="L33" s="3">
+        <v>4.7165330000000001</v>
+      </c>
+      <c r="M33" s="3">
+        <v>4.719373</v>
+      </c>
+      <c r="N33" s="3">
+        <v>4.6862599999999999</v>
+      </c>
+      <c r="O33" s="3">
+        <v>4.6849639999999999</v>
+      </c>
+      <c r="P33" s="3">
+        <v>4.684679</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>4.6858329999999997</v>
+      </c>
+      <c r="R33" s="3">
+        <v>4.6860980000000003</v>
+      </c>
+      <c r="S33" s="3">
+        <v>4.6843579999999996</v>
+      </c>
+      <c r="T33" s="3">
+        <v>4.685079</v>
+      </c>
+      <c r="U33" s="3">
+        <v>4.6852780000000003</v>
+      </c>
+      <c r="V33" s="3">
+        <v>4.6872829999999999</v>
+      </c>
+      <c r="W33" s="3">
+        <v>4.6860679999999997</v>
+      </c>
+      <c r="X33" s="3">
+        <v>4.6864150000000002</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>4.6891439999999998</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>-3.0641999999999999E-2</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>-3.1912999999999997E-2</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>-3.1780999999999997E-2</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>-3.1780999999999997E-2</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-3.0962E-2</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>-3.0894000000000001E-2</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>-3.0088E-2</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>-3.0887999999999999E-2</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-3.0533000000000001E-2</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>-3.0492999999999999E-2</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>-3.0117999999999999E-2</v>
+      </c>
+      <c r="AK33" s="3">
+        <v>-3.0228999999999999E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>10</v>
+      </c>
+      <c r="B34" s="3">
+        <v>9.4248010000000004</v>
+      </c>
+      <c r="C34" s="3">
+        <v>9.4321260000000002</v>
+      </c>
+      <c r="D34" s="3">
+        <v>9.4293309999999995</v>
+      </c>
+      <c r="E34" s="3">
+        <v>9.4334910000000001</v>
+      </c>
+      <c r="F34" s="3">
+        <v>9.4308669999999992</v>
+      </c>
+      <c r="G34" s="3">
+        <v>9.4252769999999995</v>
+      </c>
+      <c r="H34" s="3">
+        <v>9.4260819999999992</v>
+      </c>
+      <c r="I34" s="3">
+        <v>9.4288220000000003</v>
+      </c>
+      <c r="J34" s="3">
+        <v>9.4327719999999999</v>
+      </c>
+      <c r="K34" s="3">
+        <v>9.4314319999999991</v>
+      </c>
+      <c r="L34" s="3">
+        <v>9.4293849999999999</v>
+      </c>
+      <c r="M34" s="3">
+        <v>9.4369589999999999</v>
+      </c>
+      <c r="N34" s="3">
+        <v>9.3618410000000001</v>
+      </c>
+      <c r="O34" s="3">
+        <v>9.360697</v>
+      </c>
+      <c r="P34" s="3">
+        <v>9.3576689999999996</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>9.3620819999999991</v>
+      </c>
+      <c r="R34" s="3">
+        <v>9.3618810000000003</v>
+      </c>
+      <c r="S34" s="3">
+        <v>9.35581</v>
+      </c>
+      <c r="T34" s="3">
+        <v>9.3583079999999992</v>
+      </c>
+      <c r="U34" s="3">
+        <v>9.3606239999999996</v>
+      </c>
+      <c r="V34" s="3">
+        <v>9.3628309999999999</v>
+      </c>
+      <c r="W34" s="3">
+        <v>9.3618489999999994</v>
+      </c>
+      <c r="X34" s="3">
+        <v>9.3614029999999993</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>9.3668569999999995</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>-6.2959000000000001E-2</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>-7.1429000000000006E-2</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>-7.1662000000000003E-2</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>-7.1409E-2</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>-6.8985000000000005E-2</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>-6.9467000000000001E-2</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>-6.7774000000000001E-2</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>-6.8197999999999995E-2</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>-6.9941000000000003E-2</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>-6.9583000000000006E-2</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>-6.7981E-2</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>-7.0102999999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>15</v>
+      </c>
+      <c r="B35" s="3">
+        <v>14.110675000000001</v>
+      </c>
+      <c r="C35" s="3">
+        <v>14.126386</v>
+      </c>
+      <c r="D35" s="3">
+        <v>14.125458</v>
+      </c>
+      <c r="E35" s="3">
+        <v>14.130296</v>
+      </c>
+      <c r="F35" s="3">
+        <v>14.125638</v>
+      </c>
+      <c r="G35" s="3">
+        <v>14.11345</v>
+      </c>
+      <c r="H35" s="3">
+        <v>14.115016000000001</v>
+      </c>
+      <c r="I35" s="3">
+        <v>14.121547</v>
+      </c>
+      <c r="J35" s="3">
+        <v>14.127824</v>
+      </c>
+      <c r="K35" s="3">
+        <v>14.125954</v>
+      </c>
+      <c r="L35" s="3">
+        <v>14.121387</v>
+      </c>
+      <c r="M35" s="3">
+        <v>14.133305999999999</v>
+      </c>
+      <c r="N35" s="3">
+        <v>14.00428</v>
+      </c>
+      <c r="O35" s="3">
+        <v>14.018706</v>
+      </c>
+      <c r="P35" s="3">
+        <v>14.018243</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>14.023584</v>
+      </c>
+      <c r="R35" s="3">
+        <v>14.01998</v>
+      </c>
+      <c r="S35" s="3">
+        <v>14.007353</v>
+      </c>
+      <c r="T35" s="3">
+        <v>14.013021999999999</v>
+      </c>
+      <c r="U35" s="3">
+        <v>14.018314</v>
+      </c>
+      <c r="V35" s="3">
+        <v>14.021144</v>
+      </c>
+      <c r="W35" s="3">
+        <v>14.02073</v>
+      </c>
+      <c r="X35" s="3">
+        <v>14.019805</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>14.025024</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>-0.106395</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>-0.107679</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>-0.107215</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>-0.106712</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-0.105658</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>-0.106097</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>-0.101994</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>-0.10323300000000001</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-0.10668</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>-0.105224</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>-0.10158200000000001</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>-0.108281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>1</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B36" s="2">
+        <v>18.812414</v>
+      </c>
+      <c r="C36" s="2">
+        <v>18.832581999999999</v>
+      </c>
+      <c r="D36" s="2">
+        <v>18.833777999999999</v>
+      </c>
+      <c r="E36" s="3">
+        <v>18.839898000000002</v>
+      </c>
+      <c r="F36" s="3">
+        <v>18.832549</v>
+      </c>
+      <c r="G36" s="3">
+        <v>18.81352</v>
+      </c>
+      <c r="H36" s="3">
+        <v>18.817349</v>
+      </c>
+      <c r="I36" s="3">
+        <v>18.825887999999999</v>
+      </c>
+      <c r="J36" s="3">
+        <v>18.834745999999999</v>
+      </c>
+      <c r="K36" s="3">
+        <v>18.83324</v>
+      </c>
+      <c r="L36" s="3">
+        <v>18.825592</v>
+      </c>
+      <c r="M36" s="3">
+        <v>18.842582</v>
+      </c>
+      <c r="N36" s="3">
+        <v>18.669550000000001</v>
+      </c>
+      <c r="O36" s="3">
+        <v>18.689267999999998</v>
+      </c>
+      <c r="P36" s="3">
+        <v>18.688679</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>18.693197000000001</v>
+      </c>
+      <c r="R36" s="3">
+        <v>18.689867</v>
+      </c>
+      <c r="S36" s="3">
+        <v>18.668113999999999</v>
+      </c>
+      <c r="T36" s="3">
+        <v>18.679586</v>
+      </c>
+      <c r="U36" s="3">
+        <v>18.688143</v>
+      </c>
+      <c r="V36" s="3">
+        <v>18.694859000000001</v>
+      </c>
+      <c r="W36" s="3">
+        <v>18.689529</v>
+      </c>
+      <c r="X36" s="3">
+        <v>18.689264000000001</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>18.695360000000001</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>-0.14286399999999999</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>-0.143314</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>-0.14509900000000001</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>-0.1467</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>-0.142682</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>-0.14540600000000001</v>
+      </c>
+      <c r="AF36" s="3">
+        <v>-0.137762</v>
+      </c>
+      <c r="AG36" s="3">
+        <v>-0.13774500000000001</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>-0.13988700000000001</v>
+      </c>
+      <c r="AI36" s="3">
+        <v>-0.14371100000000001</v>
+      </c>
+      <c r="AJ36" s="3">
+        <v>-0.136328</v>
+      </c>
+      <c r="AK36" s="3">
+        <v>-0.14722199999999999</v>
+      </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
